--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/AgentInstitution_export.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/AgentInstitution_export.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <t>备注</t>
   </si>
@@ -114,10 +114,6 @@
   </si>
   <si>
     <t>附件个数</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>附件目录</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -525,17 +521,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17.125" style="3" customWidth="1"/>
     <col min="2" max="2" width="18.5" style="3" customWidth="1"/>
     <col min="3" max="4" width="22.25" style="3" customWidth="1"/>
     <col min="5" max="5" width="11.875" customWidth="1"/>
-    <col min="6" max="6" width="22.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>28</v>
       </c>
@@ -551,10 +546,7 @@
       <c r="E1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>0</v>
       </c>
     </row>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/AgentInstitution_export.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/AgentInstitution_export.xlsx
@@ -2,102 +2,32 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\BS3.0feature-3.0.4运营\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24180" windowHeight="13065"/>
   </bookViews>
   <sheets>
-    <sheet name="代销机构信息详细信息" sheetId="1" r:id="rId1"/>
-    <sheet name="说明" sheetId="2" r:id="rId2"/>
+    <sheet name="委托销售产品编码" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>记录状态</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>正常</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>注销</t>
-  </si>
-  <si>
-    <t>发行机构类型</t>
-  </si>
-  <si>
-    <t>国有银行</t>
-  </si>
-  <si>
-    <t>股份制银行</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>城商行</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>外资银行</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>农村合作金融机构</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>政策性银行</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>国家开发银行</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>邮政储蓄银行</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>其他</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>理财子公司</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+  <si>
+    <t>发行机构代码</t>
   </si>
   <si>
     <t>代理销售机构代码</t>
+  </si>
+  <si>
+    <t>数据状态</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -105,11 +35,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>发行机构代码</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据状态</t>
+    <t>备注</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -134,30 +60,22 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -195,26 +113,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -235,7 +147,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -277,7 +189,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -312,7 +224,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -521,166 +433,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="17.125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="18.5" style="3" customWidth="1"/>
-    <col min="3" max="4" width="22.25" style="3" customWidth="1"/>
-    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="1" max="1" width="19.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.75" style="3" customWidth="1"/>
+    <col min="4" max="4" width="19" style="3" customWidth="1"/>
+    <col min="5" max="5" width="22" style="3" customWidth="1"/>
+    <col min="6" max="6" width="18.625" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>0</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B3" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A2" s="6"/>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="27" x14ac:dyDescent="0.15">
-      <c r="A4" s="6"/>
-      <c r="B4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A5" s="6"/>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A6" s="6"/>
-      <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="27" x14ac:dyDescent="0.15">
-      <c r="A7" s="6"/>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="27" x14ac:dyDescent="0.15">
-      <c r="A8" s="6"/>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="27" x14ac:dyDescent="0.15">
-      <c r="A9" s="6"/>
-      <c r="B9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="27" x14ac:dyDescent="0.15">
-      <c r="A10" s="6"/>
-      <c r="B10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A11" s="6"/>
-      <c r="B11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="27" x14ac:dyDescent="0.15">
-      <c r="A12" s="6"/>
-      <c r="B12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A3:A12"/>
-  </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-</worksheet>
 </file>
--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/AgentInstitution_export.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/AgentInstitution_export.xlsx
@@ -5,14 +5,14 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\project\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24180" windowHeight="13065"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24180" windowHeight="13070"/>
   </bookViews>
   <sheets>
-    <sheet name="委托销售产品编码" sheetId="1" r:id="rId1"/>
+    <sheet name="代理销售机构信息" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
@@ -434,18 +434,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.75" style="3" customWidth="1"/>
+    <col min="1" max="1" width="19.26953125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.6328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7265625" style="3" customWidth="1"/>
     <col min="4" max="4" width="19" style="3" customWidth="1"/>
     <col min="5" max="5" width="22" style="3" customWidth="1"/>
-    <col min="6" max="6" width="18.625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="18.6328125" style="3" customWidth="1"/>
     <col min="7" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>2</v>
       </c>
@@ -465,7 +465,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B3" s="2"/>
     </row>
   </sheetData>
